--- a/college_rankings.xlsx
+++ b/college_rankings.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NIRF 2026 Rankings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="College Rankings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,14 +29,45 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00374151"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A73E8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00111827"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009CA3AF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -45,22 +76,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="000F4C81"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001A73E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F7FF"/>
+        <fgColor rgb="00374151"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF3FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FFFFFF"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -80,22 +150,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,6438 +550,6510 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>India Rankings 2025 – Engineering Colleges (NIRF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total Ranked Colleges: 100   |   Total Colleges: 301   |   Source: NIRF 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>College Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>RANKED COLLEGES — Top 100 (Specific NIRF Rank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Madras</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="4" t="n">
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Delhi</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>New Delhi</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="n">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Bombay</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Kanpur</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Kanpur</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="n">
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Kharagpur</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Kharagpur</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Roorkee</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Roorkee</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="n">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Hyderabad</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Guwahati</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Guwahati</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Assam</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="n">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>National Institute of Technology Tiruchirappalli</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Tiruchirappalli</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology (Banaras Hindu University) Varanasi</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Varanasi</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="n">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Birla Institute of Technology &amp; Science - Pilani</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Pilani</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Indore</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Indore</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="2" t="n">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>National Institute of Technology Rourkela</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Rourkela</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>S.R.M. Institute of Science and Technology</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="2" t="n">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology (Indian School of Mines)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Dhanbad</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Vellore Institute of Technology</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Vellore</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="2" t="n">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>National Institute of Technology Karnataka, Surathkal</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Surathkal</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Jadavpur University</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Kolkata</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="n">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Patna</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Patna</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Bihar</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Anna University</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="2" t="n">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>National Institute of Technology Calicut</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Kozhikode</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Kerala</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="4" t="n">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Siksha 'O' Anusandhan</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Bhubaneswar</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="n">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Amrita Vishwavidyapeetham</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="4" t="n">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Jamia Millia Islamia</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>New Delhi</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="n">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Gandhinagar</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Gandhinagar</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="4" t="n">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Mandi</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Mandi</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Himachal Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="2" t="n">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Jodhpur</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Jodhpur</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="4" t="n">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Warangal</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Warangal</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="2" t="n">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Thapar Institute of Engineering and Technology</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Patiala</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="4" t="n">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Delhi Technological University</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>New Delhi</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="2" t="n">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Chandigarh University</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Mohali</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="4" t="n">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Ropar</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Rupnagar</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="2" t="n">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Kalasalingam Academy of Research and Education</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Krishnan Koil</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="4" t="n">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Aligarh Muslim University</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Aligarh</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="2" t="n">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Koneru Lakshmaiah Education Foundation University (K L College of Engineering)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Vaddeswaram</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="4" t="n">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Kalinga Institute of Industrial Technology</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>Bhubaneswar</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="2" t="n">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Amity University</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Gautam Budh Nagar</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="4" t="n">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>International Institute of Information Technology Hyderabad</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="2" t="n">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Bhubaneswar</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Bhubaneswar</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="4" t="n">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Shanmugha Arts Science Technology &amp; Research Academy</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>Thanjavur</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="2" t="n">
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Institute of Chemical Technology</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="4" t="n">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Manipal Academy of Higher Education</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Manipal</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="2" t="n">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>UPES</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Dehradun</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="4" t="n">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Visvesvaraya National Institute of Technology, Nagpur</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>Nagpur</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="2" t="n">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Saveetha Institute of Medical and Technical Sciences</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="4" t="n">
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Symbiosis International</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="2" t="n">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Sri Sivasubramaniya Nadar College of Engineering</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>Kalavakkam</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="4" t="n">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Lovely Professional University</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>Phagwara</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="2" t="n">
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>National Institute of Technology Durgapur</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Durgapur</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="4" t="n">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Silchar</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>Silchar</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Assam</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="2" t="n">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Birla Institute of Technology</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Ranchi</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="4" t="n">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Graphic Era University</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Dehradun</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="2" t="n">
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>National Institute of Technology Patna</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>Patna</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Bihar</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="4" t="n">
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Engineering Science and Technology, Shibpur</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Howrah</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="2" t="n">
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Dr. B.R Ambedkar National Institute of Technology, Jalandhar</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>Jalandhar</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="4" t="n">
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Jammu</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>Jammu</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Jammu and Kashmir</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="2" t="n">
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology, Tirupati</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>Tirupati</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="4" t="n">
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Manipal University Jaipur</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>Jaipur</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="2" t="n">
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Manipal Institute of Technology</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>Manipal</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="4" t="n">
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Madan Mohan Malaviya University of Technology</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Gorakhpur</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="2" t="n">
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Space Science and Technology</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>Thiruvananthapuram</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>Kerala</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="4" t="n">
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Motilal Nehru National Institute of Technology</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>Prayagraj</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="2" t="n">
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Indraprastha Institute of Information Technology</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>New Delhi</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="4" t="n">
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Palakkad</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>Palakkad</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>Kerala</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="2" t="n">
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>National Institute of Technology Delhi</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="4" t="n">
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>Sardar Vallabhbhai National Institute of Technology</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>Surat</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="2" t="n">
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>PSG College of Technology</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="4" t="n">
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology, Andhra Pradesh</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Tadepalligudem</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2" t="n">
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>Sathyabama Institute of Science and Technology</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="4" t="n">
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>International Institute of Information Technology Bangalore</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="2" t="n">
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>Netaji Subhas University of Technology (NSUT)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="4" t="n">
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>Banasthali Vidyapith</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>Banasthali</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2" t="n">
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Bhilai</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>Durg</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>Chhattisgarh</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="4" t="n">
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Srinagar</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>Srinagar</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>Jammu and Kashmir</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="2" t="n">
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>University of Hyderabad</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="4" t="n">
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>M. S. Ramaiah Institute of Technology</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="2" t="n">
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>Christ University</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="4" t="n">
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Dharwad</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>Dharwad</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="2" t="n">
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>Rajiv Gandhi Institute of Petroleum Technology</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>Amethi</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="4" t="n">
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>Sant Longowal Institute of Engineering &amp; Technology</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>Longowal</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="2" t="n">
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>Vignan's Foundation for Science, Technology and Research</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>Guntur</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="4" t="n">
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="7" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Maulana Azad National Institute of Technology</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Bhopal</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="2" t="n">
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>National Institute of Technology, Jamshedpur</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>Jamshedpur</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="4" t="n">
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Meghalaya</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>Shillong</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Meghalaya</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="2" t="n">
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>Jain University, Bangalore</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="4" t="n">
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Kurukshetra</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>Kurukshetra</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="2" t="n">
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>National Institute of Technology, Raipur</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>Raipur</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>Chhattisgarh</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="4" t="n">
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>Vel Tech Rangarajan Dr. Sagunthala R&amp;D Institute of Science and Technology</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="2" t="n">
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>AU College of Engineering (A)</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Visakhapatnam</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="4" t="n">
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>Chitkara University</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>Rajpura</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="2" t="n">
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>COEP Technological University</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="4" t="n">
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>SR University</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>Warangal</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="2" t="n">
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>Defence Institute of Advanced Technology</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="4" t="n">
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>Panjab University</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
         <is>
           <t>Chandigarh</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>Chandigarh</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="2" t="n">
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Jawaharlal Nehru Technological University</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="4" t="n">
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="7" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>C.V. Raman Global University, Odisha</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>Bhubaneswar</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="2" t="n">
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>Atal Bihari Vajpayee Indian Institute of Information Technology and Management</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>Gwalior</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="4" t="n">
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="7" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Hamirpur</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>Hamirpur</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>Himachal Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="2" t="n">
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Pandit Deendayal Energy University</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>Gandhinagar</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="4" t="n">
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Puducherry</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>Karaikal</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>Puducherry</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>Amity University</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>North Twenty Four Parganas</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>Amity University Haryana, Gurgaon</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>Anurag University</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Telangana</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
+          <t>RANK BAND: 101–150</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Amity University</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>North Twenty Four Parganas</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>Amity University Haryana, Gurgaon</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Anurag University</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>Bansilal Ramnath Agarwal Charitable Trust's Vishwakarma Institute of Technology</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>Chandigarh Engineering College-CGC, Landran, Mohali</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>Mohali</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>Chennai Institute of Technology</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C111" s="8" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D111" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
         <is>
           <t>Coimbatore Institute of Technology</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C112" s="10" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D112" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>College of Engineering Trivandrum</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>Thiruvananthapuram</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>Kerala</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
         <is>
           <t>Dr. Vishwanath Karad MIT World Peace University</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C114" s="10" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D114" s="10" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>Easwari Engineering College</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
         <is>
           <t>Galgotias University</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C116" s="10" t="inlineStr">
         <is>
           <t>Gautam Budh Nagar</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D116" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>Gandhi Institute of Technology And Management (GITAM)</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t>Visakhapatnam</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D117" s="8" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
         <is>
           <t>Guru Gobind Singh Indraprastha University</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C118" s="10" t="inlineStr">
         <is>
           <t>New Delhi</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D118" s="10" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>Hindustan Institute of Technology and Science (HITS)</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>Indian Institute of Information Technology Allahabad</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>Prayagraj</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D120" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Technology Goa</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C121" s="8" t="inlineStr">
         <is>
           <t>Ponda</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D121" s="8" t="inlineStr">
         <is>
           <t>Goa</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
         <is>
           <t>Jawaharlal Nehru Technological University</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C122" s="10" t="inlineStr">
         <is>
           <t>Kakinada</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D122" s="10" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>Jaypee Institute of Information Technology</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C123" s="8" t="inlineStr">
         <is>
           <t>Noida</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D123" s="8" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
         <is>
           <t>K L University</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C124" s="10" t="inlineStr">
         <is>
           <t>Guntur</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D124" s="10" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>Karunya Institute of Technology and Sciences</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D125" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>Kongu Engineering College</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>Perundurai</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>KPR Institute of Engineering and Technology</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C127" s="8" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="D127" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
         <is>
           <t>Maharishi Markandeshwar</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>Ambala</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D128" s="10" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>Mahindra University</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C129" s="8" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="D129" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
         <is>
           <t>Manav Rachna International Institute of Research &amp; Studies</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>Faridabad</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D130" s="10" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>Maulana Azad National Urdu University</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C131" s="8" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D131" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
         <is>
           <t>National Institute for Solar Energy</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C132" s="10" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="D132" s="10" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>National Institute of Food Technology, Entrepreneurship &amp; Management</t>
         </is>
       </c>
-      <c r="C129" s="4" t="inlineStr">
+      <c r="C133" s="8" t="inlineStr">
         <is>
           <t>Sonepat</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D133" s="8" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
         <is>
           <t>Nirma University</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C134" s="10" t="inlineStr">
         <is>
           <t>Ahmedabad</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D134" s="10" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>Nitte Meenakshi Institute of Technology</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="C135" s="8" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="D135" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>Noida Institute of Engineering &amp; Technology</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C136" s="10" t="inlineStr">
         <is>
           <t>Greater Noida</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D136" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>Pandit Dwarka Prasad Mishra IIITDM Jabalpur</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C137" s="8" t="inlineStr">
         <is>
           <t>Jabalpur</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="D137" s="8" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>PES University</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D138" s="10" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>PSG Institute of Technology and Applied Research</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
+      <c r="C139" s="8" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="D139" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
         <is>
           <t>Punjab Engineering College (Deemed to be University), Chandigarh</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>Chandigarh</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D140" s="10" t="inlineStr">
         <is>
           <t>Chandigarh</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>R.V. College of Engineering</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
+      <c r="C141" s="8" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="D141" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
         <is>
           <t>Rajalakshmi Engineering College</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D142" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>Sharda University</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C143" s="8" t="inlineStr">
         <is>
           <t>Greater Noida</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D143" s="8" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
         <is>
           <t>Shoolini University of Biotechnology and Management Sciences</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C144" s="10" t="inlineStr">
         <is>
           <t>Solan</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D144" s="10" t="inlineStr">
         <is>
           <t>Himachal Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>Siddaganga Institute of Technology</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C145" s="8" t="inlineStr">
         <is>
           <t>Tumkur</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D145" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
         <is>
           <t>SVKM's Narsee Monjee Institute of Management Studies</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C146" s="10" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D146" s="10" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>The Northcap University</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="C147" s="8" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="D147" s="8" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B148" s="10" t="inlineStr">
         <is>
           <t>Thiagarajar College of Engineering</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C148" s="10" t="inlineStr">
         <is>
           <t>Madurai</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D148" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B145" s="5" t="inlineStr">
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>University College of Engineering</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr">
+      <c r="C149" s="8" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D145" s="4" t="inlineStr">
+      <c r="D149" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B150" s="10" t="inlineStr">
         <is>
           <t>University of Allahabad</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C150" s="10" t="inlineStr">
         <is>
           <t>Prayagraj</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D150" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="inlineStr">
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>Veermata Jijabai Technological Institute (VJTI, Mumbai)</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C151" s="8" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D151" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
         <is>
           <t>National Institute of Technology Agartala</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C152" s="10" t="inlineStr">
         <is>
           <t>Agartala</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D152" s="10" t="inlineStr">
         <is>
           <t>Tripura</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Arunachal Pradesh</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C153" s="8" t="inlineStr">
         <is>
           <t>Itanagar</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="D153" s="8" t="inlineStr">
         <is>
           <t>Arunachal Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
         <is>
           <t>National Institute of Technology Goa</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C154" s="10" t="inlineStr">
         <is>
           <t>Cuncolim</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D154" s="10" t="inlineStr">
         <is>
           <t>Goa</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>RB:101-150</t>
-        </is>
-      </c>
-      <c r="B151" s="5" t="inlineStr">
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>101-150</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Mizoram</t>
         </is>
       </c>
-      <c r="C151" s="4" t="inlineStr">
+      <c r="C155" s="8" t="inlineStr">
         <is>
           <t>Aizawl</t>
         </is>
       </c>
-      <c r="D151" s="4" t="inlineStr">
+      <c r="D155" s="8" t="inlineStr">
         <is>
           <t>Mizoram</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>RANK BAND: 151–200</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
         <is>
           <t>Amity University Rajasthan, Jaipur</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C157" s="10" t="inlineStr">
         <is>
           <t>Jaipur</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D157" s="10" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="inlineStr">
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>B. S. Abdur Rahman Crescent Institute of Science and Technology</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr">
+      <c r="C158" s="8" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr">
+      <c r="D158" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
         <is>
           <t>B.M.S. College of Engineering</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C159" s="10" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D159" s="10" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="inlineStr">
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>Bharati Vidyapeeth Deemed University College of Engineering</t>
         </is>
       </c>
-      <c r="C155" s="4" t="inlineStr">
+      <c r="C160" s="8" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="D160" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
         <is>
           <t>C M R Institute of Technology</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C161" s="10" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D161" s="10" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr">
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>CGC College of Engineering, Landran</t>
         </is>
       </c>
-      <c r="C157" s="4" t="inlineStr">
+      <c r="C162" s="8" t="inlineStr">
         <is>
           <t>Sahibzada Ajit Singh Nagar</t>
         </is>
       </c>
-      <c r="D157" s="4" t="inlineStr">
+      <c r="D162" s="8" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
         <is>
           <t>Chaitanya Bharathi Institute of Technology</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C163" s="10" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D163" s="10" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>CVR College of Engineering</t>
         </is>
       </c>
-      <c r="C159" s="4" t="inlineStr">
+      <c r="C164" s="8" t="inlineStr">
         <is>
           <t>Ibrahimpatam</t>
         </is>
       </c>
-      <c r="D159" s="4" t="inlineStr">
+      <c r="D164" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
+    <row r="165" ht="18" customHeight="1">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
         <is>
           <t>Dayalbagh Educational Institute</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C165" s="10" t="inlineStr">
         <is>
           <t>Agra</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D165" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>Dr. D. Y. Patil Institute of Technology</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
+      <c r="C166" s="8" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D161" s="4" t="inlineStr">
+      <c r="D166" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
         <is>
           <t>Dr. M. G. R. Educational and Research Institute</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C167" s="10" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D167" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="20" customHeight="1">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
+    <row r="168" ht="18" customHeight="1">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>G. L. A. University</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
+      <c r="C168" s="8" t="inlineStr">
         <is>
           <t>Mathura</t>
         </is>
       </c>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="D168" s="8" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
+    <row r="169" ht="18" customHeight="1">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
         <is>
           <t>G.L. Bajaj Institute of Technology and Management</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C169" s="10" t="inlineStr">
         <is>
           <t>Greater Noida</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D169" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="inlineStr">
+    <row r="170" ht="18" customHeight="1">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>Goka Raju Ranga Raju Institute of Engineering &amp; Technology</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr">
+      <c r="C170" s="8" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
+      <c r="D170" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="20" customHeight="1">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B171" s="10" t="inlineStr">
         <is>
           <t>Guru Ghasidas Vishwavidyalaya</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C171" s="10" t="inlineStr">
         <is>
           <t>Bilaspur</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D171" s="10" t="inlineStr">
         <is>
           <t>Chhattisgarh</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="20" customHeight="1">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
+    <row r="172" ht="18" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Information Technology, Design &amp; Manufacturing, Kancheepuram</t>
         </is>
       </c>
-      <c r="C167" s="4" t="inlineStr">
+      <c r="C172" s="8" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
+      <c r="D172" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
+    <row r="173" ht="18" customHeight="1">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
         <is>
           <t>Institute of Aeronautical Engineering</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C173" s="10" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D173" s="10" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>Institute of Engineering &amp; Management</t>
         </is>
       </c>
-      <c r="C169" s="4" t="inlineStr">
+      <c r="C174" s="8" t="inlineStr">
         <is>
           <t>Kolkata</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="D174" s="8" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B175" s="10" t="inlineStr">
         <is>
           <t>Integral University</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C175" s="10" t="inlineStr">
         <is>
           <t>Lucknow</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D175" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="inlineStr">
+    <row r="176" ht="18" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>Islamic University of Science &amp; Technology, Pulwama</t>
         </is>
       </c>
-      <c r="C171" s="4" t="inlineStr">
+      <c r="C176" s="8" t="inlineStr">
         <is>
           <t>Pulwama</t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
+      <c r="D176" s="8" t="inlineStr">
         <is>
           <t>Jammu and Kashmir</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="20" customHeight="1">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
+    <row r="177" ht="18" customHeight="1">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B177" s="10" t="inlineStr">
         <is>
           <t>J. C. Bose University of Science and Technology, YMCA</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C177" s="10" t="inlineStr">
         <is>
           <t>Faridabad</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D177" s="10" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="20" customHeight="1">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
+    <row r="178" ht="18" customHeight="1">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>Jawaharlal Nehru Technological University, Ananthapuramu</t>
         </is>
       </c>
-      <c r="C173" s="4" t="inlineStr">
+      <c r="C178" s="8" t="inlineStr">
         <is>
           <t>Ananthapuramu</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
+      <c r="D178" s="8" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
+    <row r="179" ht="18" customHeight="1">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B179" s="10" t="inlineStr">
         <is>
           <t>JSPM's Rajarshi Shahu College of Engineering</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C179" s="10" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D179" s="10" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="20" customHeight="1">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
+    <row r="180" ht="18" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>KIET Group of Institutions</t>
         </is>
       </c>
-      <c r="C175" s="4" t="inlineStr">
+      <c r="C180" s="8" t="inlineStr">
         <is>
           <t>Ghaziabad</t>
         </is>
       </c>
-      <c r="D175" s="4" t="inlineStr">
+      <c r="D180" s="8" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B181" s="10" t="inlineStr">
         <is>
           <t>KLE Technological University</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C181" s="10" t="inlineStr">
         <is>
           <t>Dharwad</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D181" s="10" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="20" customHeight="1">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="inlineStr">
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>Kumaraguru College of Technology</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C182" s="8" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="D182" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="20" customHeight="1">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
+    <row r="183" ht="18" customHeight="1">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
         <is>
           <t>Maulana Abul Kalam Azad University of Technology</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C183" s="10" t="inlineStr">
         <is>
           <t>Nadia</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D183" s="10" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="20" customHeight="1">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
+    <row r="184" ht="18" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>Mepco Schlenk Engineering College</t>
         </is>
       </c>
-      <c r="C179" s="4" t="inlineStr">
+      <c r="C184" s="8" t="inlineStr">
         <is>
           <t>Sivakasi</t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
+      <c r="D184" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="20" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
+    <row r="185" ht="18" customHeight="1">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
         <is>
           <t>National Institute of Technology Manipur</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C185" s="10" t="inlineStr">
         <is>
           <t>Imphal</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D185" s="10" t="inlineStr">
         <is>
           <t>Manipur</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="20" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B181" s="5" t="inlineStr">
+    <row r="186" ht="18" customHeight="1">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Sikkim</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C186" s="8" t="inlineStr">
         <is>
           <t>South Sikkim</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="D186" s="8" t="inlineStr">
         <is>
           <t>Sikkim</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="20" customHeight="1">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B187" s="10" t="inlineStr">
         <is>
           <t>National Institute of Technology Uttarakhand</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C187" s="10" t="inlineStr">
         <is>
           <t>Srinagar (Garhwal)</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D187" s="10" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="20" customHeight="1">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
+    <row r="188" ht="18" customHeight="1">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>National Institute of Technology Nagaland</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C188" s="8" t="inlineStr">
         <is>
           <t>Dimapur</t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="D188" s="8" t="inlineStr">
         <is>
           <t>Nagaland</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="20" customHeight="1">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
+    <row r="189" ht="18" customHeight="1">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B189" s="10" t="inlineStr">
         <is>
           <t>New Horizon College of Engineering</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C189" s="10" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D189" s="10" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="20" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>NMAM Institute of Technology</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="C190" s="8" t="inlineStr">
         <is>
           <t>Nitte, Udupi</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="D190" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
+    <row r="191" ht="18" customHeight="1">
+      <c r="A191" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B191" s="10" t="inlineStr">
         <is>
           <t>North Eastern Regional Institute of Science &amp; Technology</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C191" s="10" t="inlineStr">
         <is>
           <t>Itanagar</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D191" s="10" t="inlineStr">
         <is>
           <t>Arunachal Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="20" customHeight="1">
-      <c r="A187" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
+    <row r="192" ht="18" customHeight="1">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>R.M.K. Engineering College</t>
         </is>
       </c>
-      <c r="C187" s="4" t="inlineStr">
+      <c r="C192" s="8" t="inlineStr">
         <is>
           <t>Thiruvallur</t>
         </is>
       </c>
-      <c r="D187" s="4" t="inlineStr">
+      <c r="D192" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="20" customHeight="1">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="inlineStr">
+    <row r="193" ht="18" customHeight="1">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B193" s="10" t="inlineStr">
         <is>
           <t>Ramdeobaba University, Nagpur</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C193" s="10" t="inlineStr">
         <is>
           <t>Nagpur</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D193" s="10" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="20" customHeight="1">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
+    <row r="194" ht="18" customHeight="1">
+      <c r="A194" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>Shri Mata Vaishno Devi University</t>
         </is>
       </c>
-      <c r="C189" s="4" t="inlineStr">
+      <c r="C194" s="8" t="inlineStr">
         <is>
           <t>Katra</t>
         </is>
       </c>
-      <c r="D189" s="4" t="inlineStr">
+      <c r="D194" s="8" t="inlineStr">
         <is>
           <t>Jammu and Kashmir</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="20" customHeight="1">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
+    <row r="195" ht="18" customHeight="1">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B195" s="10" t="inlineStr">
         <is>
           <t>Sona College of Technology</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C195" s="10" t="inlineStr">
         <is>
           <t>Salem</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D195" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="20" customHeight="1">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B191" s="5" t="inlineStr">
+    <row r="196" ht="18" customHeight="1">
+      <c r="A196" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>Sri Ramakrishna Engineering College</t>
         </is>
       </c>
-      <c r="C191" s="4" t="inlineStr">
+      <c r="C196" s="8" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D191" s="4" t="inlineStr">
+      <c r="D196" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="20" customHeight="1">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
+    <row r="197" ht="18" customHeight="1">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B197" s="10" t="inlineStr">
         <is>
           <t>Sri Sai Ram Institute of Technology</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C197" s="10" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D197" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="20" customHeight="1">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B193" s="5" t="inlineStr">
+    <row r="198" ht="18" customHeight="1">
+      <c r="A198" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>Sri Sairam Engineering College</t>
         </is>
       </c>
-      <c r="C193" s="4" t="inlineStr">
+      <c r="C198" s="8" t="inlineStr">
         <is>
           <t>Kancheepuram</t>
         </is>
       </c>
-      <c r="D193" s="4" t="inlineStr">
+      <c r="D198" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="20" customHeight="1">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="inlineStr">
+    <row r="199" ht="18" customHeight="1">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B199" s="10" t="inlineStr">
         <is>
           <t>Tezpur University</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C199" s="10" t="inlineStr">
         <is>
           <t>Tezpur</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D199" s="10" t="inlineStr">
         <is>
           <t>Assam</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="20" customHeight="1">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B195" s="5" t="inlineStr">
+    <row r="200" ht="18" customHeight="1">
+      <c r="A200" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>The National Institute of Engineering</t>
         </is>
       </c>
-      <c r="C195" s="4" t="inlineStr">
+      <c r="C200" s="8" t="inlineStr">
         <is>
           <t>Mysuru</t>
         </is>
       </c>
-      <c r="D195" s="4" t="inlineStr">
+      <c r="D200" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="20" customHeight="1">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="inlineStr">
+    <row r="201" ht="18" customHeight="1">
+      <c r="A201" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B201" s="10" t="inlineStr">
         <is>
           <t>Vallurupalli Nageswara Rao Vignana Jyothi Institute of Engineering and Technology</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C201" s="10" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D201" s="10" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="20" customHeight="1">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B197" s="5" t="inlineStr">
+    <row r="202" ht="18" customHeight="1">
+      <c r="A202" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B202" s="8" t="inlineStr">
         <is>
           <t>Vardhaman College of Engineering</t>
         </is>
       </c>
-      <c r="C197" s="4" t="inlineStr">
+      <c r="C202" s="8" t="inlineStr">
         <is>
           <t>Rangareddy</t>
         </is>
       </c>
-      <c r="D197" s="4" t="inlineStr">
+      <c r="D202" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="20" customHeight="1">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="inlineStr">
+    <row r="203" ht="18" customHeight="1">
+      <c r="A203" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B203" s="10" t="inlineStr">
         <is>
           <t>Veer Surendra Sai University of Technology</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C203" s="10" t="inlineStr">
         <is>
           <t>Sambalpur</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D203" s="10" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="20" customHeight="1">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B199" s="5" t="inlineStr">
+    <row r="204" ht="18" customHeight="1">
+      <c r="A204" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B204" s="8" t="inlineStr">
         <is>
           <t>Velagapudi Ramakrishna Siddhartha Engineering College</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr">
+      <c r="C204" s="8" t="inlineStr">
         <is>
           <t>Vijayawada</t>
         </is>
       </c>
-      <c r="D199" s="4" t="inlineStr">
+      <c r="D204" s="8" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="20" customHeight="1">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
+    <row r="205" ht="18" customHeight="1">
+      <c r="A205" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B205" s="10" t="inlineStr">
         <is>
           <t>Vels Institute of Science Technology and Advanced Studies (VISTAS)</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C205" s="10" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D205" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="20" customHeight="1">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B201" s="5" t="inlineStr">
+    <row r="206" ht="18" customHeight="1">
+      <c r="A206" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B206" s="8" t="inlineStr">
         <is>
           <t>Vignan Institute of Technology and Science</t>
         </is>
       </c>
-      <c r="C201" s="4" t="inlineStr">
+      <c r="C206" s="8" t="inlineStr">
         <is>
           <t>Yadadri-Bhuvanagiri</t>
         </is>
       </c>
-      <c r="D201" s="4" t="inlineStr">
+      <c r="D206" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="20" customHeight="1">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="inlineStr">
+    <row r="207" ht="18" customHeight="1">
+      <c r="A207" s="9" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B207" s="10" t="inlineStr">
         <is>
           <t>Visvesvaraya Technological University</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C207" s="10" t="inlineStr">
         <is>
           <t>Belgaum</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D207" s="10" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="20" customHeight="1">
-      <c r="A203" s="4" t="inlineStr">
-        <is>
-          <t>RB:151-200</t>
-        </is>
-      </c>
-      <c r="B203" s="5" t="inlineStr">
+    <row r="208" ht="18" customHeight="1">
+      <c r="A208" s="11" t="inlineStr">
+        <is>
+          <t>151-200</t>
+        </is>
+      </c>
+      <c r="B208" s="8" t="inlineStr">
         <is>
           <t>Yeshwantrao Chavan College of Engineering</t>
         </is>
       </c>
-      <c r="C203" s="4" t="inlineStr">
+      <c r="C208" s="8" t="inlineStr">
         <is>
           <t>Nagpur</t>
         </is>
       </c>
-      <c r="D203" s="4" t="inlineStr">
+      <c r="D208" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="20" customHeight="1">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>Aditya Institute of Technology and Management</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>Tekkali</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="20" customHeight="1">
-      <c r="A205" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B205" s="5" t="inlineStr">
-        <is>
-          <t>Aditya University</t>
-        </is>
-      </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>Surampalem</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr">
-        <is>
-          <t>Andhra Pradesh</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="20" customHeight="1">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="inlineStr">
-        <is>
-          <t>Ajeenkya D Y Patil University</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t>Maharashtra</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="20" customHeight="1">
-      <c r="A207" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B207" s="5" t="inlineStr">
-        <is>
-          <t>Amity University Patna</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>Patna</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>Bihar</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="20" customHeight="1">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>Amity University, Gwalior</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>Gwalior</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
-        <is>
-          <t>Madhya Pradesh</t>
         </is>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B209" s="5" t="inlineStr">
+          <t>RANK BAND: 201–300</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B210" s="10" t="inlineStr">
+        <is>
+          <t>Aditya Institute of Technology and Management</t>
+        </is>
+      </c>
+      <c r="C210" s="10" t="inlineStr">
+        <is>
+          <t>Tekkali</t>
+        </is>
+      </c>
+      <c r="D210" s="10" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>Aditya University</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>Surampalem</t>
+        </is>
+      </c>
+      <c r="D211" s="8" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B212" s="10" t="inlineStr">
+        <is>
+          <t>Ajeenkya D Y Patil University</t>
+        </is>
+      </c>
+      <c r="C212" s="10" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D212" s="10" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="A213" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="inlineStr">
+        <is>
+          <t>Amity University Patna</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="A214" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B214" s="10" t="inlineStr">
+        <is>
+          <t>Amity University, Gwalior</t>
+        </is>
+      </c>
+      <c r="C214" s="10" t="inlineStr">
+        <is>
+          <t>Gwalior</t>
+        </is>
+      </c>
+      <c r="D214" s="10" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="A215" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B215" s="8" t="inlineStr">
         <is>
           <t>Amity University, Jharkhand</t>
         </is>
       </c>
-      <c r="C209" s="4" t="inlineStr">
+      <c r="C215" s="8" t="inlineStr">
         <is>
           <t>Ranchi</t>
         </is>
       </c>
-      <c r="D209" s="4" t="inlineStr">
+      <c r="D215" s="8" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="20" customHeight="1">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
+    <row r="216" ht="18" customHeight="1">
+      <c r="A216" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B216" s="10" t="inlineStr">
         <is>
           <t>Annamalai University</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C216" s="10" t="inlineStr">
         <is>
           <t>Annamalainagar</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D216" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="20" customHeight="1">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B211" s="5" t="inlineStr">
+    <row r="217" ht="18" customHeight="1">
+      <c r="A217" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="inlineStr">
         <is>
           <t>Army Institute of Technology</t>
         </is>
       </c>
-      <c r="C211" s="4" t="inlineStr">
+      <c r="C217" s="8" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D211" s="4" t="inlineStr">
+      <c r="D217" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="20" customHeight="1">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
+    <row r="218" ht="18" customHeight="1">
+      <c r="A218" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B218" s="10" t="inlineStr">
         <is>
           <t>B I T SINDRI</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C218" s="10" t="inlineStr">
         <is>
           <t>Dhanbad</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D218" s="10" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="20" customHeight="1">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
+    <row r="219" ht="18" customHeight="1">
+      <c r="A219" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
         <is>
           <t>BML Munjal University</t>
         </is>
       </c>
-      <c r="C213" s="4" t="inlineStr">
+      <c r="C219" s="8" t="inlineStr">
         <is>
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="D213" s="4" t="inlineStr">
+      <c r="D219" s="8" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="20" customHeight="1">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="inlineStr">
+    <row r="220" ht="18" customHeight="1">
+      <c r="A220" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B220" s="10" t="inlineStr">
         <is>
           <t>BMS Institute of Technology &amp; Management</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="C220" s="10" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D220" s="10" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="20" customHeight="1">
-      <c r="A215" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
+    <row r="221" ht="18" customHeight="1">
+      <c r="A221" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
         <is>
           <t>Centurion University of Technology and Management</t>
         </is>
       </c>
-      <c r="C215" s="4" t="inlineStr">
+      <c r="C221" s="8" t="inlineStr">
         <is>
           <t>Paralakhemundi</t>
         </is>
       </c>
-      <c r="D215" s="4" t="inlineStr">
+      <c r="D221" s="8" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="20" customHeight="1">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="inlineStr">
+    <row r="222" ht="18" customHeight="1">
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B222" s="10" t="inlineStr">
         <is>
           <t>Chandigarh Engineering College Jhanjeri</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
+      <c r="C222" s="10" t="inlineStr">
         <is>
           <t>Sahibzada Ajit Singh Nagar</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="D222" s="10" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="20" customHeight="1">
-      <c r="A217" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
+    <row r="223" ht="18" customHeight="1">
+      <c r="A223" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
         <is>
           <t>CMR College of Engineering &amp; Technology</t>
         </is>
       </c>
-      <c r="C217" s="4" t="inlineStr">
+      <c r="C223" s="8" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D217" s="4" t="inlineStr">
+      <c r="D223" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="20" customHeight="1">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr">
+    <row r="224" ht="18" customHeight="1">
+      <c r="A224" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B224" s="10" t="inlineStr">
         <is>
           <t>CMR Technical Campus</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="C224" s="10" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D224" s="10" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="20" customHeight="1">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B219" s="5" t="inlineStr">
+    <row r="225" ht="18" customHeight="1">
+      <c r="A225" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="inlineStr">
         <is>
           <t>College of Engineering &amp; Technology, Bhubaneswar</t>
         </is>
       </c>
-      <c r="C219" s="4" t="inlineStr">
+      <c r="C225" s="8" t="inlineStr">
         <is>
           <t>Bhubaneswar</t>
         </is>
       </c>
-      <c r="D219" s="4" t="inlineStr">
+      <c r="D225" s="8" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="20" customHeight="1">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
+    <row r="226" ht="18" customHeight="1">
+      <c r="A226" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B226" s="10" t="inlineStr">
         <is>
           <t>Dayananda Sagar College of Engineering</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="C226" s="10" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D226" s="10" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="20" customHeight="1">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B221" s="5" t="inlineStr">
+    <row r="227" ht="18" customHeight="1">
+      <c r="A227" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
         <is>
           <t>Dhirubhai Ambani Institute of Information and Communication Technology</t>
         </is>
       </c>
-      <c r="C221" s="4" t="inlineStr">
+      <c r="C227" s="8" t="inlineStr">
         <is>
           <t>Gandhinagar</t>
         </is>
       </c>
-      <c r="D221" s="4" t="inlineStr">
+      <c r="D227" s="8" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="20" customHeight="1">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="inlineStr">
+    <row r="228" ht="18" customHeight="1">
+      <c r="A228" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B228" s="10" t="inlineStr">
         <is>
           <t>Dr. Shyama Prasad Mukherjee International Institute of Information Technology, Naya Raipur</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
+      <c r="C228" s="10" t="inlineStr">
         <is>
           <t>Raipur</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="D228" s="10" t="inlineStr">
         <is>
           <t>Chhattisgarh</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="20" customHeight="1">
-      <c r="A223" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B223" s="5" t="inlineStr">
+    <row r="229" ht="18" customHeight="1">
+      <c r="A229" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
         <is>
           <t>E.G.S. Pillay Engineering College</t>
         </is>
       </c>
-      <c r="C223" s="4" t="inlineStr">
+      <c r="C229" s="8" t="inlineStr">
         <is>
           <t>Nagapattinam</t>
         </is>
       </c>
-      <c r="D223" s="4" t="inlineStr">
+      <c r="D229" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="20" customHeight="1">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
+    <row r="230" ht="18" customHeight="1">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B230" s="10" t="inlineStr">
         <is>
           <t>G. H. Raisoni College of Engineering, Nagpur</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="C230" s="10" t="inlineStr">
         <is>
           <t>Nagpur</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D230" s="10" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="20" customHeight="1">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B225" s="5" t="inlineStr">
+    <row r="231" ht="18" customHeight="1">
+      <c r="A231" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
         <is>
           <t>G. Narayanamma Institute of Technology &amp; Science for Women</t>
         </is>
       </c>
-      <c r="C225" s="4" t="inlineStr">
+      <c r="C231" s="8" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D225" s="4" t="inlineStr">
+      <c r="D231" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="20" customHeight="1">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="inlineStr">
+    <row r="232" ht="18" customHeight="1">
+      <c r="A232" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B232" s="10" t="inlineStr">
         <is>
           <t>Galgotias College of Engineering &amp; Technology</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="C232" s="10" t="inlineStr">
         <is>
           <t>Greater Noida</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D232" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="20" customHeight="1">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B227" s="5" t="inlineStr">
+    <row r="233" ht="18" customHeight="1">
+      <c r="A233" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
         <is>
           <t>Gandhi Institute for Technological Advancement (GITA), Bhubaneswar</t>
         </is>
       </c>
-      <c r="C227" s="4" t="inlineStr">
+      <c r="C233" s="8" t="inlineStr">
         <is>
           <t>Bhubaneswar</t>
         </is>
       </c>
-      <c r="D227" s="4" t="inlineStr">
+      <c r="D233" s="8" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="20" customHeight="1">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
+    <row r="234" ht="18" customHeight="1">
+      <c r="A234" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B234" s="10" t="inlineStr">
         <is>
           <t>GIET University, Gunupur</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
+      <c r="C234" s="10" t="inlineStr">
         <is>
           <t>Gunupur</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="D234" s="10" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="20" customHeight="1">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B229" s="5" t="inlineStr">
+    <row r="235" ht="18" customHeight="1">
+      <c r="A235" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
         <is>
           <t>GMR Institute of Technology</t>
         </is>
       </c>
-      <c r="C229" s="4" t="inlineStr">
+      <c r="C235" s="8" t="inlineStr">
         <is>
           <t>Rajahmundry</t>
         </is>
       </c>
-      <c r="D229" s="4" t="inlineStr">
+      <c r="D235" s="8" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="230" ht="20" customHeight="1">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="inlineStr">
+    <row r="236" ht="18" customHeight="1">
+      <c r="A236" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B236" s="10" t="inlineStr">
         <is>
           <t>Godavari Institute of Engineering &amp; Technology</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C236" s="10" t="inlineStr">
         <is>
           <t>Rajahmundry</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D236" s="10" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="231" ht="20" customHeight="1">
-      <c r="A231" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B231" s="5" t="inlineStr">
+    <row r="237" ht="18" customHeight="1">
+      <c r="A237" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
         <is>
           <t>Guru Jambheshwar University of Science and Technology, Hisar</t>
         </is>
       </c>
-      <c r="C231" s="4" t="inlineStr">
+      <c r="C237" s="8" t="inlineStr">
         <is>
           <t>Hisar</t>
         </is>
       </c>
-      <c r="D231" s="4" t="inlineStr">
+      <c r="D237" s="8" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="232" ht="20" customHeight="1">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
+    <row r="238" ht="18" customHeight="1">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B238" s="10" t="inlineStr">
         <is>
           <t>Harcourt Butler Technical University</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="C238" s="10" t="inlineStr">
         <is>
           <t>Kanpur Nagar</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="D238" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="233" ht="20" customHeight="1">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B233" s="5" t="inlineStr">
+    <row r="239" ht="18" customHeight="1">
+      <c r="A239" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
         <is>
           <t>Hindusthan College of Engineering and Technology</t>
         </is>
       </c>
-      <c r="C233" s="4" t="inlineStr">
+      <c r="C239" s="8" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D233" s="4" t="inlineStr">
+      <c r="D239" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="234" ht="20" customHeight="1">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="inlineStr">
+    <row r="240" ht="18" customHeight="1">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B240" s="10" t="inlineStr">
         <is>
           <t>IES College of Technology, Bhopal</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
+      <c r="C240" s="10" t="inlineStr">
         <is>
           <t>Bhopal</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="D240" s="10" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="235" ht="20" customHeight="1">
-      <c r="A235" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B235" s="5" t="inlineStr">
+    <row r="241" ht="18" customHeight="1">
+      <c r="A241" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
         <is>
           <t>Indian Institute of Information Technology Guwahati</t>
         </is>
       </c>
-      <c r="C235" s="4" t="inlineStr">
+      <c r="C241" s="8" t="inlineStr">
         <is>
           <t>Guwahati</t>
         </is>
       </c>
-      <c r="D235" s="4" t="inlineStr">
+      <c r="D241" s="8" t="inlineStr">
         <is>
           <t>Assam</t>
         </is>
       </c>
     </row>
-    <row r="236" ht="20" customHeight="1">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="inlineStr">
+    <row r="242" ht="18" customHeight="1">
+      <c r="A242" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B242" s="10" t="inlineStr">
         <is>
           <t>Indian Institute of Petroleum &amp; Energy</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="C242" s="10" t="inlineStr">
         <is>
           <t>Visakhapatnam</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="D242" s="10" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="237" ht="20" customHeight="1">
-      <c r="A237" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B237" s="5" t="inlineStr">
+    <row r="243" ht="18" customHeight="1">
+      <c r="A243" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
         <is>
           <t>Indira Gandhi Delhi Technical University for Women</t>
         </is>
       </c>
-      <c r="C237" s="4" t="inlineStr">
+      <c r="C243" s="8" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="D237" s="4" t="inlineStr">
+      <c r="D243" s="8" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
     </row>
-    <row r="238" ht="20" customHeight="1">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="inlineStr">
+    <row r="244" ht="18" customHeight="1">
+      <c r="A244" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B244" s="10" t="inlineStr">
         <is>
           <t>Jamia Hamdard</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C244" s="10" t="inlineStr">
         <is>
           <t>New Delhi</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="D244" s="10" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
     </row>
-    <row r="239" ht="20" customHeight="1">
-      <c r="A239" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+    <row r="245" ht="18" customHeight="1">
+      <c r="A245" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
         <is>
           <t>Jaypee University of Information Technology</t>
         </is>
       </c>
-      <c r="C239" s="4" t="inlineStr">
+      <c r="C245" s="8" t="inlineStr">
         <is>
           <t>Solan</t>
         </is>
       </c>
-      <c r="D239" s="4" t="inlineStr">
+      <c r="D245" s="8" t="inlineStr">
         <is>
           <t>Himachal Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="20" customHeight="1">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
+    <row r="246" ht="18" customHeight="1">
+      <c r="A246" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B246" s="10" t="inlineStr">
         <is>
           <t>JIS College of Engineering</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C246" s="10" t="inlineStr">
         <is>
           <t>Kalyani</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D246" s="10" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
     </row>
-    <row r="241" ht="20" customHeight="1">
-      <c r="A241" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B241" s="5" t="inlineStr">
+    <row r="247" ht="18" customHeight="1">
+      <c r="A247" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
         <is>
           <t>JSS Academy Of Technical Education, Noida</t>
         </is>
       </c>
-      <c r="C241" s="4" t="inlineStr">
+      <c r="C247" s="8" t="inlineStr">
         <is>
           <t>Gautam Budh Nagar</t>
         </is>
       </c>
-      <c r="D241" s="4" t="inlineStr">
+      <c r="D247" s="8" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="242" ht="20" customHeight="1">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="inlineStr">
+    <row r="248" ht="18" customHeight="1">
+      <c r="A248" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B248" s="10" t="inlineStr">
         <is>
           <t>JSS Science and Technology University</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="C248" s="10" t="inlineStr">
         <is>
           <t>Mysuru</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="D248" s="10" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="243" ht="20" customHeight="1">
-      <c r="A243" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
+    <row r="249" ht="18" customHeight="1">
+      <c r="A249" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="inlineStr">
         <is>
           <t>K. Ramakrishnan College of Engineering</t>
         </is>
       </c>
-      <c r="C243" s="4" t="inlineStr">
+      <c r="C249" s="8" t="inlineStr">
         <is>
           <t>Samayapuram</t>
         </is>
       </c>
-      <c r="D243" s="4" t="inlineStr">
+      <c r="D249" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="244" ht="20" customHeight="1">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="inlineStr">
+    <row r="250" ht="18" customHeight="1">
+      <c r="A250" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B250" s="10" t="inlineStr">
         <is>
           <t>K. Ramakrishnan College of Technology</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr">
+      <c r="C250" s="10" t="inlineStr">
         <is>
           <t>Tiruchirappalli</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="D250" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="245" ht="20" customHeight="1">
-      <c r="A245" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B245" s="5" t="inlineStr">
+    <row r="251" ht="18" customHeight="1">
+      <c r="A251" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
         <is>
           <t>Kakatiya Institute of Technology &amp; Science</t>
         </is>
       </c>
-      <c r="C245" s="4" t="inlineStr">
+      <c r="C251" s="8" t="inlineStr">
         <is>
           <t>Warangal</t>
         </is>
       </c>
-      <c r="D245" s="4" t="inlineStr">
+      <c r="D251" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="246" ht="20" customHeight="1">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="inlineStr">
+    <row r="252" ht="18" customHeight="1">
+      <c r="A252" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B252" s="10" t="inlineStr">
         <is>
           <t>Kalaignar Karunanidhi Institute of Technology</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
+      <c r="C252" s="10" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="D252" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="247" ht="20" customHeight="1">
-      <c r="A247" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B247" s="5" t="inlineStr">
+    <row r="253" ht="18" customHeight="1">
+      <c r="A253" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
         <is>
           <t>Karpagam College of Engineering</t>
         </is>
       </c>
-      <c r="C247" s="4" t="inlineStr">
+      <c r="C253" s="8" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D247" s="4" t="inlineStr">
+      <c r="D253" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="248" ht="20" customHeight="1">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="inlineStr">
+    <row r="254" ht="18" customHeight="1">
+      <c r="A254" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B254" s="10" t="inlineStr">
         <is>
           <t>Lakshmi Narain College of Technology</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="C254" s="10" t="inlineStr">
         <is>
           <t>Bhopal</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="D254" s="10" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="249" ht="20" customHeight="1">
-      <c r="A249" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B249" s="5" t="inlineStr">
+    <row r="255" ht="18" customHeight="1">
+      <c r="A255" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="inlineStr">
         <is>
           <t>M. Kumarasamy College of Engineering</t>
         </is>
       </c>
-      <c r="C249" s="4" t="inlineStr">
+      <c r="C255" s="8" t="inlineStr">
         <is>
           <t>Karur</t>
         </is>
       </c>
-      <c r="D249" s="4" t="inlineStr">
+      <c r="D255" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="20" customHeight="1">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="inlineStr">
+    <row r="256" ht="18" customHeight="1">
+      <c r="A256" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B256" s="10" t="inlineStr">
         <is>
           <t>Madanapalle Institute of Technology &amp; Science</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
+      <c r="C256" s="10" t="inlineStr">
         <is>
           <t>Madanapalle</t>
         </is>
       </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="D256" s="10" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="251" ht="20" customHeight="1">
-      <c r="A251" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B251" s="5" t="inlineStr">
+    <row r="257" ht="18" customHeight="1">
+      <c r="A257" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="inlineStr">
         <is>
           <t>Maharaja Sayajirao University of Baroda</t>
         </is>
       </c>
-      <c r="C251" s="4" t="inlineStr">
+      <c r="C257" s="8" t="inlineStr">
         <is>
           <t>Vadodara</t>
         </is>
       </c>
-      <c r="D251" s="4" t="inlineStr">
+      <c r="D257" s="8" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
     </row>
-    <row r="252" ht="20" customHeight="1">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="inlineStr">
+    <row r="258" ht="18" customHeight="1">
+      <c r="A258" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B258" s="10" t="inlineStr">
         <is>
           <t>Maharshi Dayanand University, Rohtak</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
+      <c r="C258" s="10" t="inlineStr">
         <is>
           <t>Rohtak</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="D258" s="10" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="253" ht="20" customHeight="1">
-      <c r="A253" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B253" s="5" t="inlineStr">
+    <row r="259" ht="18" customHeight="1">
+      <c r="A259" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="inlineStr">
         <is>
           <t>Maharshi Karve Stree Shikshan Samstha's Cummins College of Engineering for Women</t>
         </is>
       </c>
-      <c r="C253" s="4" t="inlineStr">
+      <c r="C259" s="8" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D253" s="4" t="inlineStr">
+      <c r="D259" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="254" ht="20" customHeight="1">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="inlineStr">
+    <row r="260" ht="18" customHeight="1">
+      <c r="A260" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B260" s="10" t="inlineStr">
         <is>
           <t>Mahatma Jyotiba Phule Rohilkhand University, Bareilly</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C260" s="10" t="inlineStr">
         <is>
           <t>Bareilly</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="D260" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="255" ht="20" customHeight="1">
-      <c r="A255" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B255" s="5" t="inlineStr">
+    <row r="261" ht="18" customHeight="1">
+      <c r="A261" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="inlineStr">
         <is>
           <t>Malla Reddy Engineering College</t>
         </is>
       </c>
-      <c r="C255" s="4" t="inlineStr">
+      <c r="C261" s="8" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D255" s="4" t="inlineStr">
+      <c r="D261" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="256" ht="20" customHeight="1">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="inlineStr">
+    <row r="262" ht="18" customHeight="1">
+      <c r="A262" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B262" s="10" t="inlineStr">
         <is>
           <t>Malla Reddy Engineering College for Women (Autonomous)</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="C262" s="10" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="D262" s="10" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="257" ht="20" customHeight="1">
-      <c r="A257" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B257" s="5" t="inlineStr">
+    <row r="263" ht="18" customHeight="1">
+      <c r="A263" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="inlineStr">
         <is>
           <t>Manav Rachna University</t>
         </is>
       </c>
-      <c r="C257" s="4" t="inlineStr">
+      <c r="C263" s="8" t="inlineStr">
         <is>
           <t>Faridabad</t>
         </is>
       </c>
-      <c r="D257" s="4" t="inlineStr">
+      <c r="D263" s="8" t="inlineStr">
         <is>
           <t>Haryana</t>
         </is>
       </c>
     </row>
-    <row r="258" ht="20" customHeight="1">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="inlineStr">
+    <row r="264" ht="18" customHeight="1">
+      <c r="A264" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B264" s="10" t="inlineStr">
         <is>
           <t>Marwadi University</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="C264" s="10" t="inlineStr">
         <is>
           <t>Rajkot</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="D264" s="10" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
     </row>
-    <row r="259" ht="20" customHeight="1">
-      <c r="A259" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B259" s="5" t="inlineStr">
+    <row r="265" ht="18" customHeight="1">
+      <c r="A265" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B265" s="8" t="inlineStr">
         <is>
           <t>MIT Art, Design and Technology University, Pune</t>
         </is>
       </c>
-      <c r="C259" s="4" t="inlineStr">
+      <c r="C265" s="8" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D259" s="4" t="inlineStr">
+      <c r="D265" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="260" ht="20" customHeight="1">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B260" s="3" t="inlineStr">
+    <row r="266" ht="18" customHeight="1">
+      <c r="A266" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B266" s="10" t="inlineStr">
         <is>
           <t>MLR Institute of Technology</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
+      <c r="C266" s="10" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="D266" s="10" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="20" customHeight="1">
-      <c r="A261" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
+    <row r="267" ht="18" customHeight="1">
+      <c r="A267" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="inlineStr">
         <is>
           <t>Narula Institute of Technology</t>
         </is>
       </c>
-      <c r="C261" s="4" t="inlineStr">
+      <c r="C267" s="8" t="inlineStr">
         <is>
           <t>Kolkata</t>
         </is>
       </c>
-      <c r="D261" s="4" t="inlineStr">
+      <c r="D267" s="8" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
     </row>
-    <row r="262" ht="20" customHeight="1">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="inlineStr">
+    <row r="268" ht="18" customHeight="1">
+      <c r="A268" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B268" s="10" t="inlineStr">
         <is>
           <t>National Engineering College</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
+      <c r="C268" s="10" t="inlineStr">
         <is>
           <t>Kovilpatti</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="D268" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="263" ht="20" customHeight="1">
-      <c r="A263" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B263" s="5" t="inlineStr">
+    <row r="269" ht="18" customHeight="1">
+      <c r="A269" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B269" s="8" t="inlineStr">
         <is>
           <t>National Institute of Advanced Manufacturing Technology, Ranchi</t>
         </is>
       </c>
-      <c r="C263" s="4" t="inlineStr">
+      <c r="C269" s="8" t="inlineStr">
         <is>
           <t>Ranchi</t>
         </is>
       </c>
-      <c r="D263" s="4" t="inlineStr">
+      <c r="D269" s="8" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
     </row>
-    <row r="264" ht="20" customHeight="1">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="inlineStr">
+    <row r="270" ht="18" customHeight="1">
+      <c r="A270" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B270" s="10" t="inlineStr">
+        <is>
+          <t>National Institute Of Technology, Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="C270" s="10" t="inlineStr">
+        <is>
+          <t>Tadepalligudem</t>
+        </is>
+      </c>
+      <c r="D270" s="10" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="18" customHeight="1">
+      <c r="A271" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="inlineStr">
         <is>
           <t>P E S College of Engineering, MANDYA</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C271" s="8" t="inlineStr">
         <is>
           <t>Mandya</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="D271" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="265" ht="20" customHeight="1">
-      <c r="A265" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
+    <row r="272" ht="18" customHeight="1">
+      <c r="A272" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B272" s="10" t="inlineStr">
         <is>
           <t>Padmashree Dr. D.Y. Patil Vidyapeeth, Mumbai</t>
         </is>
       </c>
-      <c r="C265" s="4" t="inlineStr">
+      <c r="C272" s="10" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="D265" s="4" t="inlineStr">
+      <c r="D272" s="10" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="266" ht="20" customHeight="1">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="inlineStr">
+    <row r="273" ht="18" customHeight="1">
+      <c r="A273" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
         <is>
           <t>Panimalar Engineering College</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr">
+      <c r="C273" s="8" t="inlineStr">
         <is>
           <t>Thiruvallur</t>
         </is>
       </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="D273" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="267" ht="20" customHeight="1">
-      <c r="A267" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
+    <row r="274" ht="18" customHeight="1">
+      <c r="A274" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B274" s="10" t="inlineStr">
         <is>
           <t>Pimpri Chinchwad College of Engineering</t>
         </is>
       </c>
-      <c r="C267" s="4" t="inlineStr">
+      <c r="C274" s="10" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D267" s="4" t="inlineStr">
+      <c r="D274" s="10" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="268" ht="20" customHeight="1">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="inlineStr">
+    <row r="275" ht="18" customHeight="1">
+      <c r="A275" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B275" s="8" t="inlineStr">
         <is>
           <t>Prasad V Potluri Siddhartha Institute of Technology</t>
         </is>
       </c>
-      <c r="C268" s="2" t="inlineStr">
+      <c r="C275" s="8" t="inlineStr">
         <is>
           <t>Vijayawada</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="D275" s="8" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="269" ht="20" customHeight="1">
-      <c r="A269" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
+    <row r="276" ht="18" customHeight="1">
+      <c r="A276" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B276" s="10" t="inlineStr">
         <is>
           <t>Presidency University, Bengaluru</t>
         </is>
       </c>
-      <c r="C269" s="4" t="inlineStr">
+      <c r="C276" s="10" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D269" s="4" t="inlineStr">
+      <c r="D276" s="10" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="270" ht="20" customHeight="1">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
+    <row r="277" ht="18" customHeight="1">
+      <c r="A277" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B277" s="8" t="inlineStr">
         <is>
           <t>Prince Shri Venkateshwara Padmavathy Engineering College</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr">
+      <c r="C277" s="8" t="inlineStr">
         <is>
           <t>Kancheepuram</t>
         </is>
       </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="D277" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="271" ht="20" customHeight="1">
-      <c r="A271" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
+    <row r="278" ht="18" customHeight="1">
+      <c r="A278" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B278" s="10" t="inlineStr">
         <is>
           <t>PSNA College of Engineering and Technology, Dindigul</t>
         </is>
       </c>
-      <c r="C271" s="4" t="inlineStr">
+      <c r="C278" s="10" t="inlineStr">
         <is>
           <t>Dindigul</t>
         </is>
       </c>
-      <c r="D271" s="4" t="inlineStr">
+      <c r="D278" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="272" ht="20" customHeight="1">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B272" s="3" t="inlineStr">
+    <row r="279" ht="18" customHeight="1">
+      <c r="A279" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B279" s="8" t="inlineStr">
         <is>
           <t>Puducherry Technological University</t>
         </is>
       </c>
-      <c r="C272" s="2" t="inlineStr">
+      <c r="C279" s="8" t="inlineStr">
         <is>
           <t>Puducherry</t>
         </is>
       </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="D279" s="8" t="inlineStr">
         <is>
           <t>Pondicherry</t>
         </is>
       </c>
     </row>
-    <row r="273" ht="20" customHeight="1">
-      <c r="A273" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B273" s="5" t="inlineStr">
+    <row r="280" ht="18" customHeight="1">
+      <c r="A280" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B280" s="10" t="inlineStr">
         <is>
           <t>QIS College of Engineering &amp; Technology</t>
         </is>
       </c>
-      <c r="C273" s="4" t="inlineStr">
+      <c r="C280" s="10" t="inlineStr">
         <is>
           <t>Ongole</t>
         </is>
       </c>
-      <c r="D273" s="4" t="inlineStr">
+      <c r="D280" s="10" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="274" ht="20" customHeight="1">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
+    <row r="281" ht="18" customHeight="1">
+      <c r="A281" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B281" s="8" t="inlineStr">
         <is>
           <t>R. M. K. College of Engineering and Technology</t>
         </is>
       </c>
-      <c r="C274" s="2" t="inlineStr">
+      <c r="C281" s="8" t="inlineStr">
         <is>
           <t>Thiruvallur</t>
         </is>
       </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="D281" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="275" ht="20" customHeight="1">
-      <c r="A275" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B275" s="5" t="inlineStr">
+    <row r="282" ht="18" customHeight="1">
+      <c r="A282" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B282" s="10" t="inlineStr">
         <is>
           <t>R.M.D Engineering College</t>
         </is>
       </c>
-      <c r="C275" s="4" t="inlineStr">
+      <c r="C282" s="10" t="inlineStr">
         <is>
           <t>Thiruvallur</t>
         </is>
       </c>
-      <c r="D275" s="4" t="inlineStr">
+      <c r="D282" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="276" ht="20" customHeight="1">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="inlineStr">
+    <row r="283" ht="18" customHeight="1">
+      <c r="A283" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B283" s="8" t="inlineStr">
         <is>
           <t>Rabindranath Tagore University</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr">
+      <c r="C283" s="8" t="inlineStr">
         <is>
           <t>Raisen</t>
         </is>
       </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="D283" s="8" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="277" ht="20" customHeight="1">
-      <c r="A277" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B277" s="5" t="inlineStr">
+    <row r="284" ht="18" customHeight="1">
+      <c r="A284" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B284" s="10" t="inlineStr">
         <is>
           <t>Rajalakshmi Institute of Technology</t>
         </is>
       </c>
-      <c r="C277" s="4" t="inlineStr">
+      <c r="C284" s="10" t="inlineStr">
         <is>
           <t>Thiruvallur</t>
         </is>
       </c>
-      <c r="D277" s="4" t="inlineStr">
+      <c r="D284" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="278" ht="20" customHeight="1">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="inlineStr">
+    <row r="285" ht="18" customHeight="1">
+      <c r="A285" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="inlineStr">
         <is>
           <t>Rajeev Gandhi Memorial College of Engineering &amp; Technology</t>
         </is>
       </c>
-      <c r="C278" s="2" t="inlineStr">
+      <c r="C285" s="8" t="inlineStr">
         <is>
           <t>Nandyal</t>
         </is>
       </c>
-      <c r="D278" s="2" t="inlineStr">
+      <c r="D285" s="8" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="279" ht="20" customHeight="1">
-      <c r="A279" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B279" s="5" t="inlineStr">
+    <row r="286" ht="18" customHeight="1">
+      <c r="A286" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B286" s="10" t="inlineStr">
         <is>
           <t>Rathinam Technical Campus</t>
         </is>
       </c>
-      <c r="C279" s="4" t="inlineStr">
+      <c r="C286" s="10" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D279" s="4" t="inlineStr">
+      <c r="D286" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="280" ht="20" customHeight="1">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B280" s="3" t="inlineStr">
+    <row r="287" ht="18" customHeight="1">
+      <c r="A287" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="inlineStr">
         <is>
           <t>Reva University</t>
         </is>
       </c>
-      <c r="C280" s="2" t="inlineStr">
+      <c r="C287" s="8" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="D287" s="8" t="inlineStr">
         <is>
           <t>Karnataka</t>
         </is>
       </c>
     </row>
-    <row r="281" ht="20" customHeight="1">
-      <c r="A281" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B281" s="5" t="inlineStr">
+    <row r="288" ht="18" customHeight="1">
+      <c r="A288" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B288" s="10" t="inlineStr">
         <is>
           <t>Saveetha Engineering College</t>
         </is>
       </c>
-      <c r="C281" s="4" t="inlineStr">
+      <c r="C288" s="10" t="inlineStr">
         <is>
           <t>Sriperumbudur</t>
         </is>
       </c>
-      <c r="D281" s="4" t="inlineStr">
+      <c r="D288" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="282" ht="20" customHeight="1">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B282" s="3" t="inlineStr">
+    <row r="289" ht="18" customHeight="1">
+      <c r="A289" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B289" s="8" t="inlineStr">
         <is>
           <t>Shri Vile Parle Kelavani Mandal's Dwarkadas J. Sanghvi College of Engineering</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr">
+      <c r="C289" s="8" t="inlineStr">
         <is>
           <t>Mumbai Suburban</t>
         </is>
       </c>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="D289" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="283" ht="20" customHeight="1">
-      <c r="A283" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B283" s="5" t="inlineStr">
+    <row r="290" ht="18" customHeight="1">
+      <c r="A290" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B290" s="10" t="inlineStr">
         <is>
           <t>Sikkim Manipal Institute of Technology (SMIT)</t>
         </is>
       </c>
-      <c r="C283" s="4" t="inlineStr">
+      <c r="C290" s="10" t="inlineStr">
         <is>
           <t>Rangpo</t>
         </is>
       </c>
-      <c r="D283" s="4" t="inlineStr">
+      <c r="D290" s="10" t="inlineStr">
         <is>
           <t>Sikkim</t>
         </is>
       </c>
     </row>
-    <row r="284" ht="20" customHeight="1">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B284" s="3" t="inlineStr">
+    <row r="291" ht="18" customHeight="1">
+      <c r="A291" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B291" s="8" t="inlineStr">
         <is>
           <t>Silicon University, Odisha, Bhubaneswar</t>
         </is>
       </c>
-      <c r="C284" s="2" t="inlineStr">
+      <c r="C291" s="8" t="inlineStr">
         <is>
           <t>Bhubaneswar</t>
         </is>
       </c>
-      <c r="D284" s="2" t="inlineStr">
+      <c r="D291" s="8" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
     </row>
-    <row r="285" ht="20" customHeight="1">
-      <c r="A285" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B285" s="5" t="inlineStr">
+    <row r="292" ht="18" customHeight="1">
+      <c r="A292" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B292" s="10" t="inlineStr">
         <is>
           <t>SNS College of Technology</t>
         </is>
       </c>
-      <c r="C285" s="4" t="inlineStr">
+      <c r="C292" s="10" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D285" s="4" t="inlineStr">
+      <c r="D292" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="286" ht="20" customHeight="1">
-      <c r="A286" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B286" s="3" t="inlineStr">
+    <row r="293" ht="18" customHeight="1">
+      <c r="A293" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B293" s="8" t="inlineStr">
         <is>
           <t>Sree Vidyanikethan Engineering College</t>
         </is>
       </c>
-      <c r="C286" s="2" t="inlineStr">
+      <c r="C293" s="8" t="inlineStr">
         <is>
           <t>Tirupati</t>
         </is>
       </c>
-      <c r="D286" s="2" t="inlineStr">
+      <c r="D293" s="8" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="287" ht="20" customHeight="1">
-      <c r="A287" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B287" s="5" t="inlineStr">
+    <row r="294" ht="18" customHeight="1">
+      <c r="A294" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B294" s="10" t="inlineStr">
         <is>
           <t>Sri Eshwar College of Engineering</t>
         </is>
       </c>
-      <c r="C287" s="4" t="inlineStr">
+      <c r="C294" s="10" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="D287" s="4" t="inlineStr">
+      <c r="D294" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="288" ht="20" customHeight="1">
-      <c r="A288" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B288" s="3" t="inlineStr">
+    <row r="295" ht="18" customHeight="1">
+      <c r="A295" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B295" s="8" t="inlineStr">
         <is>
           <t>Sri Manakula Vinayagar Engineering College</t>
         </is>
       </c>
-      <c r="C288" s="2" t="inlineStr">
+      <c r="C295" s="8" t="inlineStr">
         <is>
           <t>Puducherry</t>
         </is>
       </c>
-      <c r="D288" s="2" t="inlineStr">
+      <c r="D295" s="8" t="inlineStr">
         <is>
           <t>Pondicherry</t>
         </is>
       </c>
     </row>
-    <row r="289" ht="20" customHeight="1">
-      <c r="A289" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B289" s="5" t="inlineStr">
+    <row r="296" ht="18" customHeight="1">
+      <c r="A296" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B296" s="10" t="inlineStr">
         <is>
           <t>Sri Venkateswara College of Engineering</t>
         </is>
       </c>
-      <c r="C289" s="4" t="inlineStr">
+      <c r="C296" s="10" t="inlineStr">
         <is>
           <t>Sriperumbudur</t>
         </is>
       </c>
-      <c r="D289" s="4" t="inlineStr">
+      <c r="D296" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="290" ht="20" customHeight="1">
-      <c r="A290" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B290" s="3" t="inlineStr">
+    <row r="297" ht="18" customHeight="1">
+      <c r="A297" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B297" s="8" t="inlineStr">
         <is>
           <t>Sri Venkateswara College of Engineering and Technology</t>
         </is>
       </c>
-      <c r="C290" s="2" t="inlineStr">
+      <c r="C297" s="8" t="inlineStr">
         <is>
           <t>Chittoor</t>
         </is>
       </c>
-      <c r="D290" s="2" t="inlineStr">
+      <c r="D297" s="8" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="291" ht="20" customHeight="1">
-      <c r="A291" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B291" s="5" t="inlineStr">
+    <row r="298" ht="18" customHeight="1">
+      <c r="A298" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B298" s="10" t="inlineStr">
         <is>
           <t>Sri Venkateswara College of Engineering, Tirupati</t>
         </is>
       </c>
-      <c r="C291" s="4" t="inlineStr">
+      <c r="C298" s="10" t="inlineStr">
         <is>
           <t>Tirupati</t>
         </is>
       </c>
-      <c r="D291" s="4" t="inlineStr">
+      <c r="D298" s="10" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="292" ht="20" customHeight="1">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B292" s="3" t="inlineStr">
+    <row r="299" ht="18" customHeight="1">
+      <c r="A299" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B299" s="8" t="inlineStr">
         <is>
           <t>Sri Venkateswara University</t>
         </is>
       </c>
-      <c r="C292" s="2" t="inlineStr">
+      <c r="C299" s="8" t="inlineStr">
         <is>
           <t>Tirupati</t>
         </is>
       </c>
-      <c r="D292" s="2" t="inlineStr">
+      <c r="D299" s="8" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="293" ht="20" customHeight="1">
-      <c r="A293" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+    <row r="300" ht="18" customHeight="1">
+      <c r="A300" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B300" s="10" t="inlineStr">
         <is>
           <t>St. Joseph's Institute of Technology</t>
         </is>
       </c>
-      <c r="C293" s="4" t="inlineStr">
+      <c r="C300" s="10" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D293" s="4" t="inlineStr">
+      <c r="D300" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="294" ht="20" customHeight="1">
-      <c r="A294" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B294" s="3" t="inlineStr">
+    <row r="301" ht="18" customHeight="1">
+      <c r="A301" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B301" s="8" t="inlineStr">
         <is>
           <t>St. Josephs College of Engineering</t>
         </is>
       </c>
-      <c r="C294" s="2" t="inlineStr">
+      <c r="C301" s="8" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
-      <c r="D294" s="2" t="inlineStr">
+      <c r="D301" s="8" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
-    <row r="295" ht="20" customHeight="1">
-      <c r="A295" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B295" s="5" t="inlineStr">
+    <row r="302" ht="18" customHeight="1">
+      <c r="A302" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B302" s="10" t="inlineStr">
         <is>
           <t>Teerthanker Mahaveer University</t>
         </is>
       </c>
-      <c r="C295" s="4" t="inlineStr">
+      <c r="C302" s="10" t="inlineStr">
         <is>
           <t>Moradabad</t>
         </is>
       </c>
-      <c r="D295" s="4" t="inlineStr">
+      <c r="D302" s="10" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="296" ht="20" customHeight="1">
-      <c r="A296" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B296" s="3" t="inlineStr">
+    <row r="303" ht="18" customHeight="1">
+      <c r="A303" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B303" s="8" t="inlineStr">
         <is>
           <t>The LNM Institute of Information Technology, Jaipur</t>
         </is>
       </c>
-      <c r="C296" s="2" t="inlineStr">
+      <c r="C303" s="8" t="inlineStr">
         <is>
           <t>Jaipur</t>
         </is>
       </c>
-      <c r="D296" s="2" t="inlineStr">
+      <c r="D303" s="8" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
     </row>
-    <row r="297" ht="20" customHeight="1">
-      <c r="A297" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B297" s="5" t="inlineStr">
+    <row r="304" ht="18" customHeight="1">
+      <c r="A304" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B304" s="10" t="inlineStr">
         <is>
           <t>Uttaranchal University</t>
         </is>
       </c>
-      <c r="C297" s="4" t="inlineStr">
+      <c r="C304" s="10" t="inlineStr">
         <is>
           <t>Dehradun</t>
         </is>
       </c>
-      <c r="D297" s="4" t="inlineStr">
+      <c r="D304" s="10" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
     </row>
-    <row r="298" ht="20" customHeight="1">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B298" s="3" t="inlineStr">
+    <row r="305" ht="18" customHeight="1">
+      <c r="A305" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B305" s="8" t="inlineStr">
         <is>
           <t>Vidya Jyothi Institute of Technology</t>
         </is>
       </c>
-      <c r="C298" s="2" t="inlineStr">
+      <c r="C305" s="8" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="D298" s="2" t="inlineStr">
+      <c r="D305" s="8" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="20" customHeight="1">
-      <c r="A299" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B299" s="5" t="inlineStr">
+    <row r="306" ht="18" customHeight="1">
+      <c r="A306" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B306" s="10" t="inlineStr">
         <is>
           <t>Vignan's Institute of Information Technology</t>
         </is>
       </c>
-      <c r="C299" s="4" t="inlineStr">
+      <c r="C306" s="10" t="inlineStr">
         <is>
           <t>Visakhapatnam</t>
         </is>
       </c>
-      <c r="D299" s="4" t="inlineStr">
+      <c r="D306" s="10" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
-    <row r="300" ht="20" customHeight="1">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B300" s="3" t="inlineStr">
+    <row r="307" ht="18" customHeight="1">
+      <c r="A307" s="11" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B307" s="8" t="inlineStr">
         <is>
           <t>Walchand College of Engineering</t>
         </is>
       </c>
-      <c r="C300" s="2" t="inlineStr">
+      <c r="C307" s="8" t="inlineStr">
         <is>
           <t>Sangli</t>
         </is>
       </c>
-      <c r="D300" s="2" t="inlineStr">
+      <c r="D307" s="8" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
     </row>
-    <row r="301" ht="20" customHeight="1">
-      <c r="A301" s="4" t="inlineStr">
-        <is>
-          <t>RB:201-300</t>
-        </is>
-      </c>
-      <c r="B301" s="5" t="inlineStr">
+    <row r="308" ht="18" customHeight="1">
+      <c r="A308" s="9" t="inlineStr">
+        <is>
+          <t>201-300</t>
+        </is>
+      </c>
+      <c r="B308" s="10" t="inlineStr">
         <is>
           <t>National Institute of Food Technology, Entrepreneurship and Management - Thanjavur (NIFTEM)</t>
         </is>
       </c>
-      <c r="C301" s="4" t="inlineStr">
+      <c r="C308" s="10" t="inlineStr">
         <is>
           <t>Thanjavur</t>
         </is>
       </c>
-      <c r="D301" s="4" t="inlineStr">
+      <c r="D308" s="10" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A209:D209"/>
+    <mergeCell ref="A156:D156"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>